--- a/dataset/02.wo_Defects/uninit_pointer.xlsx
+++ b/dataset/02.wo_Defects/uninit_pointer.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>char ** uninit_pointer_016_gbl_doubleptr; uninit_pointer_014_s_001 *s; TWO } values; extern volatile int vflag; void uninit_pointer_016() { int flag=0,i; char *s=(char*) malloc(10*sizeof(char)); if(uninit_pointer_016_func_001(flag)==0) { uninit_pointer_016_func_002(); } if(uninit_pointer_016_gbl_doubleptr!=NULL) { for(i=0;i&lt;10;i++) { if(uninit_pointer_016_gbl_doubleptr[i] !=NULL) { if(i==7) { printf("unint p %s \n",uninit_pointer_016_gbl_doubleptr[i]); strcpy(s,uninit_pointer_016_gbl_doubleptr[i]); /*Tool should not detect this line as error*/ /*No ERROR:Uninitialized pointer*/ printf("unint p %s \n",s); } free (uninit_pointer_016_gbl_doubleptr[i]); } } free(uninit_pointer_016_gbl_doubleptr); free(s); } } void uninit_pointer_016_func_002() { int i; if(uninit_pointer_016_func_001(0)==0) { uninit_pointer_016_gbl_doubleptr=(char**) malloc(10*sizeof(char*)); for(i=0;i&lt;10;i++) { uninit_pointer_016_gbl_doubleptr[i]=(char*) malloc(10*sizeof(char)); strcpy(uninit_pointer_016_gbl_doubleptr[i],"STRING00"); } } } int uninit_pointer_016_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>char ** uninit_pointer_016_gbl_doubleptr; uninit_pointer_014_s_001 *s; TWO } values; extern volatile int vflag; void uninit_pointer_016() { int flag=0,i; char *s=(char*) malloc(10*sizeof(char)); if(uninit_pointer_016_func_001(flag)==0) { uninit_pointer_016_func_002(); } if(uninit_pointer_016_gbl_doubleptr!=NULL) { for(i=0;i&lt;10;i++) { if(uninit_pointer_016_gbl_doubleptr[i] !=NULL) { if(i==7) { printf("unint p %s \n",uninit_pointer_016_gbl_doubleptr[i]); strcpy(s,uninit_pointer_016_gbl_doubleptr[i]); /*Tool should not detect this line as error*/ /*No ERROR:Uninitialized pointer*/ printf("unint p %s \n",s); } free (uninit_pointer_016_gbl_doubleptr[i]); } } free(uninit_pointer_016_gbl_doubleptr); free(s); } } int uninit_pointer_016_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void uninit_pointer_016_func_002() { int i; if(uninit_pointer_016_func_001(0)==0) { uninit_pointer_016_gbl_doubleptr=(char**) malloc(10*sizeof(char*)); for(i=0;i&lt;10;i++) { uninit_pointer_016_gbl_doubleptr[i]=(char*) malloc(10*sizeof(char)); strcpy(uninit_pointer_016_gbl_doubleptr[i],"STRING00"); } } }</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
